--- a/config.xlsx
+++ b/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\02_SmartCards\02_Prod\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3201A4-17B3-44E4-8C3A-1FDAFDB26134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A81D308-F974-413B-AC51-BFE0A67DCD6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8100" yWindow="0" windowWidth="15036" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Anzeigename</t>
   </si>
@@ -28,10 +28,16 @@
     <t>Dateiname</t>
   </si>
   <si>
-    <t>SmartCards_Einmaleins.xlsx</t>
-  </si>
-  <si>
     <t>Sissis 1 x 1</t>
+  </si>
+  <si>
+    <t>smartcards_1x1.xlsx</t>
+  </si>
+  <si>
+    <t>smartcards_Testdecks.xlsx</t>
+  </si>
+  <si>
+    <t>Verschiedenes</t>
   </si>
 </sst>
 </file>
@@ -377,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -394,10 +400,18 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>2</v>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\02_SmartCards\02_Prod\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A81D308-F974-413B-AC51-BFE0A67DCD6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B51929E5-9E38-4FBD-B2BA-878A182BD49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4260" yWindow="6048" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Anzeigename</t>
   </si>
@@ -34,10 +34,16 @@
     <t>smartcards_1x1.xlsx</t>
   </si>
   <si>
-    <t>smartcards_Testdecks.xlsx</t>
-  </si>
-  <si>
-    <t>Verschiedenes</t>
+    <t>Sissi</t>
+  </si>
+  <si>
+    <t>smartcards_Sissi.xlsx</t>
+  </si>
+  <si>
+    <t>smartcards_Ludwig.xlsx</t>
+  </si>
+  <si>
+    <t>Ludwig</t>
   </si>
 </sst>
 </file>
@@ -383,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -408,10 +414,18 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/config.xlsx
+++ b/config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\02_SmartCards\02_Prod\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\02_SmartCards\02_Prod\Sissi_4hG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B51929E5-9E38-4FBD-B2BA-878A182BD49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE61EAE7-F023-44D9-99D5-F5A275F8E30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4260" yWindow="6048" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -28,22 +28,22 @@
     <t>Dateiname</t>
   </si>
   <si>
-    <t>Sissis 1 x 1</t>
-  </si>
-  <si>
     <t>smartcards_1x1.xlsx</t>
   </si>
   <si>
-    <t>Sissi</t>
-  </si>
-  <si>
-    <t>smartcards_Sissi.xlsx</t>
-  </si>
-  <si>
-    <t>smartcards_Ludwig.xlsx</t>
-  </si>
-  <si>
     <t>Ludwig</t>
+  </si>
+  <si>
+    <t>1 x 1</t>
+  </si>
+  <si>
+    <t>Beispiele</t>
+  </si>
+  <si>
+    <t>smartcards_Beispiele.xlsx</t>
+  </si>
+  <si>
+    <t>smartcards_Mathe1.xlsx</t>
   </si>
 </sst>
 </file>
@@ -406,10 +406,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -417,15 +417,15 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\02_SmartCards\02_Prod\Sissi_4hG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE61EAE7-F023-44D9-99D5-F5A275F8E30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD3E556-9BD3-4098-84E5-9BE92AC176DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -31,9 +31,6 @@
     <t>smartcards_1x1.xlsx</t>
   </si>
   <si>
-    <t>Ludwig</t>
-  </si>
-  <si>
     <t>1 x 1</t>
   </si>
   <si>
@@ -44,6 +41,9 @@
   </si>
   <si>
     <t>smartcards_Mathe1.xlsx</t>
+  </si>
+  <si>
+    <t>Mathe 1</t>
   </si>
 </sst>
 </file>
@@ -406,15 +406,15 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -422,10 +422,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
